--- a/phase-01/expert-inputs/expert-2.xlsx
+++ b/phase-01/expert-inputs/expert-2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Works\VSU\ProjectManagment\phase-01\expert-inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CE94FCA-4224-4124-89CA-EFD08BBDEEB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{261C4660-5BF6-4748-AE5D-2A5E62267791}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Инструкция" sheetId="1" r:id="rId1"/>
@@ -35,53 +35,23 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="49">
   <si>
     <t>Индивидуальная анкета · участник 2</t>
   </si>
   <si>
-    <t>ДЕМОНСТРАЦИОННЫЕ СУЖДЕНИЯ из исходной книги. Перед использованием замените или лично подтвердите значения.</t>
-  </si>
-  <si>
     <t>ФИО участника</t>
   </si>
   <si>
-    <t>[впишите ФИО]</t>
-  </si>
-  <si>
     <t>Дата оценивания</t>
   </si>
   <si>
-    <t>[впишите дату]</t>
-  </si>
-  <si>
     <t>Версия документов</t>
   </si>
   <si>
     <t>Фаза 1 · 4 концепции · 12 UC каждая · K1–K5</t>
   </si>
   <si>
-    <t>Статус анкеты</t>
-  </si>
-  <si>
-    <t>ДЕМО / НЕ ПОДТВЕРЖДЕНО</t>
-  </si>
-  <si>
-    <t>Порядок работы</t>
-  </si>
-  <si>
-    <t>1. Изучите паспорта A1–A4 и criteria.docx.</t>
-  </si>
-  <si>
-    <t>2. Независимо заполните 25 баллов TOPSIS на листе TOPSIS_оценки, столбец E.</t>
-  </si>
-  <si>
-    <t>3. Независимо заполните 40 суждений МАИ на листе МАИ_сравнения, столбец E.</t>
-  </si>
-  <si>
-    <t>4. Укажите ФИО, дату и сохраните файл; сообщите координатору.</t>
-  </si>
-  <si>
     <t>Шкала TOPSIS</t>
   </si>
   <si>
@@ -91,9 +61,6 @@
     <t>Шкала МАИ</t>
   </si>
   <si>
-    <t>1,2,3,…,9 или обратные 1/2,…,1/9; для 1/3 вводите формулу =1/3.</t>
-  </si>
-  <si>
     <t>Перенос в общую книгу</t>
   </si>
   <si>
@@ -106,24 +73,9 @@
     <t>Копируйте только значения; не заменяйте столбцы H:J / H с формулами.</t>
   </si>
   <si>
-    <t>Важно</t>
-  </si>
-  <si>
-    <t>Это ручная передача, автоматической связи с тремя внешними файлами нет.</t>
-  </si>
-  <si>
-    <t>Контроль</t>
-  </si>
-  <si>
-    <t>«ЗАПОЛНЕНО» означает проверку формата и числа ответов, НЕ факт участия эксперта.</t>
-  </si>
-  <si>
     <t>TOPSIS · 25 балльных оценок · эксперт 2</t>
   </si>
   <si>
-    <t>Синий столбец E — демонстрационные значения. Поменяйте на собственные баллы 1–9 и проверьте отметки справа.</t>
-  </si>
-  <si>
     <t>Тип</t>
   </si>
   <si>
@@ -199,9 +151,6 @@
     <t>МАИ · 40 попарных сравнений · эксперт 2</t>
   </si>
   <si>
-    <t>В столбце E укажите, во сколько раз ЛЕВЫЙ элемент предпочтительнее ПРАВОГО. =1/3 означает, что правый предпочтительнее.</t>
-  </si>
-  <si>
     <t>Матрица</t>
   </si>
   <si>
@@ -224,6 +173,15 @@
   </si>
   <si>
     <t>Корректных строк / 40:</t>
+  </si>
+  <si>
+    <t>Лошаков Максим Алекссевич</t>
+  </si>
+  <si>
+    <t>12.10.2026</t>
+  </si>
+  <si>
+    <t>1,2,3,…,9 или обратные 1/2,…,1/9</t>
   </si>
 </sst>
 </file>
@@ -233,7 +191,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -242,11 +200,6 @@
       <b/>
       <sz val="15"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF824400"/>
       <name val="Carlito"/>
     </font>
     <font>
@@ -276,7 +229,7 @@
       <name val="Carlito"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -290,17 +243,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEDD5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFE5F1FE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF3D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -320,38 +263,32 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -566,7 +503,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -588,23 +525,25 @@
       <c r="F1" s="9"/>
       <c r="G1" s="9"/>
     </row>
-    <row r="3" spans="1:7" ht="36" customHeight="1">
-      <c r="A3" s="10" t="s">
+    <row r="4" spans="1:7" ht="38.4" customHeight="1">
+      <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-    </row>
-    <row r="5" spans="1:7" ht="38.4" customHeight="1">
+      <c r="B4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" ht="48" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -612,12 +551,12 @@
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
     </row>
-    <row r="6" spans="1:7" ht="48" customHeight="1">
+    <row r="6" spans="1:7" ht="60" customHeight="1">
       <c r="A6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>4</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -625,25 +564,21 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
     </row>
-    <row r="7" spans="1:7" ht="60" customHeight="1">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>7</v>
-      </c>
+    <row r="7" spans="1:7" ht="24" customHeight="1">
+      <c r="A7" s="1"/>
+      <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
     </row>
-    <row r="8" spans="1:7" ht="24" customHeight="1">
+    <row r="8" spans="1:7" ht="51.6" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>9</v>
+        <v>5</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -651,32 +586,34 @@
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
     </row>
-    <row r="9" spans="1:7" ht="24" customHeight="1">
-      <c r="A9" s="1"/>
-      <c r="B9" s="2"/>
+    <row r="9" spans="1:7" ht="58.8" customHeight="1">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>48</v>
+      </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
     </row>
-    <row r="10" spans="1:7" ht="46.8" customHeight="1">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>11</v>
-      </c>
+    <row r="10" spans="1:7" ht="24" customHeight="1">
+      <c r="A10" s="1"/>
+      <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
     </row>
-    <row r="11" spans="1:7" ht="70.8" customHeight="1">
-      <c r="A11" s="1"/>
+    <row r="11" spans="1:7" ht="44.4" customHeight="1">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="B11" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -684,10 +621,10 @@
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
     </row>
-    <row r="12" spans="1:7" ht="50.4" customHeight="1">
+    <row r="12" spans="1:7" ht="72" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -695,10 +632,10 @@
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
     </row>
-    <row r="13" spans="1:7" ht="64.2" customHeight="1">
+    <row r="13" spans="1:7" ht="58.8" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -706,110 +643,9 @@
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
     </row>
-    <row r="14" spans="1:7" ht="24" customHeight="1">
-      <c r="A14" s="1"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7" ht="51.6" customHeight="1">
-      <c r="A15" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:7" ht="58.8" customHeight="1">
-      <c r="A16" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:7" ht="24" customHeight="1">
-      <c r="A17" s="1"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7" ht="44.4" customHeight="1">
-      <c r="A18" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="1:7" ht="72" customHeight="1">
-      <c r="A19" s="1"/>
-      <c r="B19" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="1:7" ht="58.8" customHeight="1">
-      <c r="A20" s="1"/>
-      <c r="B20" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-    </row>
-    <row r="21" spans="1:7" ht="60" customHeight="1">
-      <c r="A21" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-    </row>
-    <row r="22" spans="1:7" ht="56.4" customHeight="1">
-      <c r="A22" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A3:G3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -817,7 +653,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -831,7 +667,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="33" customHeight="1">
       <c r="A1" s="9" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -840,77 +676,88 @@
       <c r="F1" s="9"/>
       <c r="G1" s="9"/>
     </row>
-    <row r="3" spans="1:7" ht="36" customHeight="1">
-      <c r="A3" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-    </row>
-    <row r="4" spans="1:7" ht="31.95" customHeight="1">
-      <c r="A4" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>35</v>
-      </c>
+    <row r="3" spans="1:7" ht="31.95" customHeight="1">
+      <c r="A3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="22.95" customHeight="1">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="5">
+        <v>8</v>
+      </c>
+      <c r="F4" s="6" t="str">
+        <f t="shared" ref="F4:F28" si="0">IF(E4="","ПУСТО",IF(AND(ISNUMBER(E4),E4&gt;=1,E4&lt;=9,MOD(E4,1)=0),"OK","ОШИБКА"))</f>
+        <v>OK</v>
+      </c>
+      <c r="G4" s="7"/>
     </row>
     <row r="5" spans="1:7" ht="22.95" customHeight="1">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="E5" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" s="6" t="str">
-        <f t="shared" ref="F5:F29" si="0">IF(E5="","ПУСТО",IF(AND(ISNUMBER(E5),E5&gt;=1,E5&lt;=9,MOD(E5,1)=0),"OK","ОШИБКА"))</f>
+        <f t="shared" si="0"/>
         <v>OK</v>
       </c>
       <c r="G5" s="7"/>
     </row>
     <row r="6" spans="1:7" ht="22.95" customHeight="1">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="E6" s="5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F6" s="6" t="str">
         <f t="shared" si="0"/>
@@ -920,16 +767,16 @@
     </row>
     <row r="7" spans="1:7" ht="22.95" customHeight="1">
       <c r="A7" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="E7" s="5">
         <v>7</v>
@@ -942,19 +789,19 @@
     </row>
     <row r="8" spans="1:7" ht="22.95" customHeight="1">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="E8" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F8" s="6" t="str">
         <f t="shared" si="0"/>
@@ -964,19 +811,19 @@
     </row>
     <row r="9" spans="1:7" ht="22.95" customHeight="1">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="E9" s="5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F9" s="6" t="str">
         <f t="shared" si="0"/>
@@ -986,16 +833,16 @@
     </row>
     <row r="10" spans="1:7" ht="22.95" customHeight="1">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="E10" s="5">
         <v>8</v>
@@ -1008,19 +855,19 @@
     </row>
     <row r="11" spans="1:7" ht="22.95" customHeight="1">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="E11" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1030,16 +877,16 @@
     </row>
     <row r="12" spans="1:7" ht="22.95" customHeight="1">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="E12" s="5">
         <v>9</v>
@@ -1052,19 +899,19 @@
     </row>
     <row r="13" spans="1:7" ht="22.95" customHeight="1">
       <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" t="s">
         <v>30</v>
       </c>
-      <c r="B13" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13" t="s">
-        <v>44</v>
-      </c>
       <c r="D13" s="2" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="E13" s="5">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F13" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1074,19 +921,19 @@
     </row>
     <row r="14" spans="1:7" ht="22.95" customHeight="1">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="E14" s="5">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F14" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1096,19 +943,19 @@
     </row>
     <row r="15" spans="1:7" ht="22.95" customHeight="1">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="E15" s="5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F15" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1118,19 +965,19 @@
     </row>
     <row r="16" spans="1:7" ht="22.95" customHeight="1">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="E16" s="5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F16" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1140,19 +987,19 @@
     </row>
     <row r="17" spans="1:7" ht="22.95" customHeight="1">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="C17" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="E17" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F17" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1162,19 +1009,19 @@
     </row>
     <row r="18" spans="1:7" ht="22.95" customHeight="1">
       <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" t="s">
         <v>30</v>
       </c>
-      <c r="B18" t="s">
-        <v>49</v>
-      </c>
-      <c r="C18" t="s">
-        <v>44</v>
-      </c>
       <c r="D18" s="2" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="E18" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F18" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1184,19 +1031,19 @@
     </row>
     <row r="19" spans="1:7" ht="22.95" customHeight="1">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="C19" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="E19" s="5">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F19" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1206,19 +1053,19 @@
     </row>
     <row r="20" spans="1:7" ht="22.95" customHeight="1">
       <c r="A20" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="C20" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="E20" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F20" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1228,16 +1075,16 @@
     </row>
     <row r="21" spans="1:7" ht="22.95" customHeight="1">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="C21" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="E21" s="5">
         <v>8</v>
@@ -1250,19 +1097,19 @@
     </row>
     <row r="22" spans="1:7" ht="22.95" customHeight="1">
       <c r="A22" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="C22" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="E22" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F22" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1272,19 +1119,19 @@
     </row>
     <row r="23" spans="1:7" ht="22.95" customHeight="1">
       <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" t="s">
         <v>30</v>
       </c>
-      <c r="B23" t="s">
-        <v>50</v>
-      </c>
-      <c r="C23" t="s">
-        <v>44</v>
-      </c>
       <c r="D23" s="2" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="E23" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F23" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1294,19 +1141,19 @@
     </row>
     <row r="24" spans="1:7" ht="22.95" customHeight="1">
       <c r="A24" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="C24" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="E24" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F24" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1316,19 +1163,19 @@
     </row>
     <row r="25" spans="1:7" ht="22.95" customHeight="1">
       <c r="A25" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="C25" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="E25" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F25" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1338,19 +1185,19 @@
     </row>
     <row r="26" spans="1:7" ht="22.95" customHeight="1">
       <c r="A26" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="C26" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="E26" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F26" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1360,16 +1207,16 @@
     </row>
     <row r="27" spans="1:7" ht="22.95" customHeight="1">
       <c r="A27" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="C27" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="E27" s="5">
         <v>7</v>
@@ -1382,19 +1229,19 @@
     </row>
     <row r="28" spans="1:7" ht="22.95" customHeight="1">
       <c r="A28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" t="s">
         <v>30</v>
       </c>
-      <c r="B28" t="s">
-        <v>51</v>
-      </c>
-      <c r="C28" t="s">
-        <v>44</v>
-      </c>
       <c r="D28" s="2" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="E28" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F28" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1402,48 +1249,25 @@
       </c>
       <c r="G28" s="7"/>
     </row>
-    <row r="29" spans="1:7" ht="22.95" customHeight="1">
-      <c r="A29" t="s">
-        <v>30</v>
-      </c>
-      <c r="B29" t="s">
-        <v>51</v>
-      </c>
-      <c r="C29" t="s">
-        <v>46</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E29" s="5">
-        <v>8</v>
-      </c>
-      <c r="F29" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="G29" s="7"/>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="D31" t="s">
-        <v>52</v>
-      </c>
-      <c r="E31">
-        <f>COUNTIF(F5:F29,"OK")</f>
+    <row r="30" spans="1:7">
+      <c r="D30" t="s">
+        <v>36</v>
+      </c>
+      <c r="E30">
+        <f>COUNTIF(F4:F28,"OK")</f>
         <v>25</v>
       </c>
-      <c r="F31" t="str">
-        <f>IF(E31=25,"ЗАПОЛНЕНО","ПРОВЕРИТЬ")</f>
+      <c r="F30" t="str">
+        <f>IF(E30=25,"ЗАПОЛНЕНО","ПРОВЕРИТЬ")</f>
         <v>ЗАПОЛНЕНО</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A3:G3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="E5:E29" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" sqref="E4:E28" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"1,2,3,4,5,6,7,8,9"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1453,7 +1277,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -1466,7 +1290,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="33" customHeight="1">
       <c r="A1" s="9" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -1475,77 +1299,88 @@
       <c r="F1" s="9"/>
       <c r="G1" s="9"/>
     </row>
-    <row r="3" spans="1:7" ht="36" customHeight="1">
-      <c r="A3" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-    </row>
-    <row r="4" spans="1:7" ht="31.95" customHeight="1">
-      <c r="A4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>35</v>
-      </c>
+    <row r="3" spans="1:7" ht="31.95" customHeight="1">
+      <c r="A3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="22.05" customHeight="1">
+      <c r="A4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="8">
+        <v>1</v>
+      </c>
+      <c r="F4" s="6" t="str">
+        <f t="shared" ref="F4:F43" si="0">IF(E4="","ПУСТО",IF(E4&lt;=0,"ОШИБКА",IF(OR(AND(E4&gt;=1,E4&lt;=9,MOD(E4,1)=0),AND(E4&gt;=1/9,E4&lt;1,ABS(1/E4-ROUND(1/E4,0))&lt;0.000001)),"OK","ОШИБКА")))</f>
+        <v>OK</v>
+      </c>
+      <c r="G4" s="7"/>
     </row>
     <row r="5" spans="1:7" ht="22.05" customHeight="1">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="E5" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="6" t="str">
-        <f t="shared" ref="F5:F44" si="0">IF(E5="","ПУСТО",IF(E5&lt;=0,"ОШИБКА",IF(OR(AND(E5&gt;=1,E5&lt;=9,MOD(E5,1)=0),AND(E5&gt;=1/9,E5&lt;1,ABS(1/E5-ROUND(1/E5,0))&lt;0.000001)),"OK","ОШИБКА")))</f>
+        <f t="shared" si="0"/>
         <v>OK</v>
       </c>
       <c r="G5" s="7"/>
     </row>
     <row r="6" spans="1:7" ht="22.05" customHeight="1">
       <c r="A6" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="E6" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1555,16 +1390,16 @@
     </row>
     <row r="7" spans="1:7" ht="22.05" customHeight="1">
       <c r="A7" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="E7" s="8">
         <v>3</v>
@@ -1577,19 +1412,19 @@
     </row>
     <row r="8" spans="1:7" ht="22.05" customHeight="1">
       <c r="A8" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="E8" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1599,19 +1434,19 @@
     </row>
     <row r="9" spans="1:7" ht="22.05" customHeight="1">
       <c r="A9" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="E9" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1621,19 +1456,19 @@
     </row>
     <row r="10" spans="1:7" ht="22.05" customHeight="1">
       <c r="A10" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="E10" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1643,19 +1478,19 @@
     </row>
     <row r="11" spans="1:7" ht="22.05" customHeight="1">
       <c r="A11" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D11" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="E11" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F11" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1665,16 +1500,16 @@
     </row>
     <row r="12" spans="1:7" ht="22.05" customHeight="1">
       <c r="A12" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="E12" s="8">
         <v>2</v>
@@ -1687,16 +1522,16 @@
     </row>
     <row r="13" spans="1:7" ht="22.05" customHeight="1">
       <c r="A13" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="D13" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="E13" s="8">
         <v>2</v>
@@ -1709,19 +1544,19 @@
     </row>
     <row r="14" spans="1:7" ht="22.05" customHeight="1">
       <c r="A14" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D14" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="E14" s="8">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="F14" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1731,19 +1566,19 @@
     </row>
     <row r="15" spans="1:7" ht="22.05" customHeight="1">
       <c r="A15" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D15" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E15" s="8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F15" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1753,19 +1588,19 @@
     </row>
     <row r="16" spans="1:7" ht="22.05" customHeight="1">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D16" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E16" s="8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F16" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1775,19 +1610,19 @@
     </row>
     <row r="17" spans="1:7" ht="22.05" customHeight="1">
       <c r="A17" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="D17" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="E17" s="8">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="F17" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1797,19 +1632,19 @@
     </row>
     <row r="18" spans="1:7" ht="22.05" customHeight="1">
       <c r="A18" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="D18" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E18" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F18" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1819,19 +1654,19 @@
     </row>
     <row r="19" spans="1:7" ht="22.05" customHeight="1">
       <c r="A19" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="D19" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="E19" s="8">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="F19" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1841,19 +1676,19 @@
     </row>
     <row r="20" spans="1:7" ht="22.05" customHeight="1">
       <c r="A20" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="D20" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="E20" s="8">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="F20" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1863,19 +1698,19 @@
     </row>
     <row r="21" spans="1:7" ht="22.05" customHeight="1">
       <c r="A21" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D21" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E21" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F21" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1885,19 +1720,19 @@
     </row>
     <row r="22" spans="1:7" ht="22.05" customHeight="1">
       <c r="A22" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="B22" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="C22" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D22" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E22" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F22" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1907,19 +1742,19 @@
     </row>
     <row r="23" spans="1:7" ht="22.05" customHeight="1">
       <c r="A23" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="C23" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="D23" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="E23" s="8">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="F23" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1929,19 +1764,19 @@
     </row>
     <row r="24" spans="1:7" ht="22.05" customHeight="1">
       <c r="A24" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="C24" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="D24" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E24" s="8">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="F24" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1951,19 +1786,19 @@
     </row>
     <row r="25" spans="1:7" ht="22.05" customHeight="1">
       <c r="A25" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="C25" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="D25" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="E25" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F25" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1973,19 +1808,19 @@
     </row>
     <row r="26" spans="1:7" ht="22.05" customHeight="1">
       <c r="A26" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="C26" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="D26" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="E26" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F26" s="6" t="str">
         <f t="shared" si="0"/>
@@ -1995,19 +1830,19 @@
     </row>
     <row r="27" spans="1:7" ht="22.05" customHeight="1">
       <c r="A27" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="C27" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D27" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E27" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" s="6" t="str">
         <f t="shared" si="0"/>
@@ -2017,19 +1852,19 @@
     </row>
     <row r="28" spans="1:7" ht="22.05" customHeight="1">
       <c r="A28" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="C28" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D28" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E28" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F28" s="6" t="str">
         <f t="shared" si="0"/>
@@ -2039,19 +1874,19 @@
     </row>
     <row r="29" spans="1:7" ht="22.05" customHeight="1">
       <c r="A29" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="D29" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="E29" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F29" s="6" t="str">
         <f t="shared" si="0"/>
@@ -2061,19 +1896,19 @@
     </row>
     <row r="30" spans="1:7" ht="22.05" customHeight="1">
       <c r="A30" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="B30" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="C30" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="D30" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E30" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F30" s="6" t="str">
         <f t="shared" si="0"/>
@@ -2083,19 +1918,19 @@
     </row>
     <row r="31" spans="1:7" ht="22.05" customHeight="1">
       <c r="A31" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="B31" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="C31" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="D31" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="E31" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F31" s="6" t="str">
         <f t="shared" si="0"/>
@@ -2105,19 +1940,19 @@
     </row>
     <row r="32" spans="1:7" ht="22.05" customHeight="1">
       <c r="A32" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="C32" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="D32" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="E32" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F32" s="6" t="str">
         <f t="shared" si="0"/>
@@ -2127,19 +1962,19 @@
     </row>
     <row r="33" spans="1:7" ht="22.05" customHeight="1">
       <c r="A33" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="B33" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="C33" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D33" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E33" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" s="6" t="str">
         <f t="shared" si="0"/>
@@ -2149,19 +1984,19 @@
     </row>
     <row r="34" spans="1:7" ht="22.05" customHeight="1">
       <c r="A34" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="B34" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="C34" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D34" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E34" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F34" s="6" t="str">
         <f t="shared" si="0"/>
@@ -2171,19 +2006,19 @@
     </row>
     <row r="35" spans="1:7" ht="22.05" customHeight="1">
       <c r="A35" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="B35" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="C35" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="D35" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="E35" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F35" s="6" t="str">
         <f t="shared" si="0"/>
@@ -2193,19 +2028,19 @@
     </row>
     <row r="36" spans="1:7" ht="22.05" customHeight="1">
       <c r="A36" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="C36" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="D36" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E36" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F36" s="6" t="str">
         <f t="shared" si="0"/>
@@ -2215,19 +2050,19 @@
     </row>
     <row r="37" spans="1:7" ht="22.05" customHeight="1">
       <c r="A37" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="B37" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="C37" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="D37" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="E37" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F37" s="6" t="str">
         <f t="shared" si="0"/>
@@ -2237,19 +2072,19 @@
     </row>
     <row r="38" spans="1:7" ht="22.05" customHeight="1">
       <c r="A38" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="B38" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="C38" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="D38" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="E38" s="8">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="F38" s="6" t="str">
         <f t="shared" si="0"/>
@@ -2259,19 +2094,19 @@
     </row>
     <row r="39" spans="1:7" ht="22.05" customHeight="1">
       <c r="A39" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="B39" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="C39" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D39" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E39" s="8">
-        <v>0.25</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="F39" s="6" t="str">
         <f t="shared" si="0"/>
@@ -2281,19 +2116,19 @@
     </row>
     <row r="40" spans="1:7" ht="22.05" customHeight="1">
       <c r="A40" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="B40" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="C40" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D40" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E40" s="8">
-        <v>0.33333333333333331</v>
+        <v>0.25</v>
       </c>
       <c r="F40" s="6" t="str">
         <f t="shared" si="0"/>
@@ -2303,19 +2138,19 @@
     </row>
     <row r="41" spans="1:7" ht="22.05" customHeight="1">
       <c r="A41" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="B41" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="C41" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="D41" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="E41" s="8">
-        <v>0.25</v>
+        <v>2</v>
       </c>
       <c r="F41" s="6" t="str">
         <f t="shared" si="0"/>
@@ -2325,19 +2160,19 @@
     </row>
     <row r="42" spans="1:7" ht="22.05" customHeight="1">
       <c r="A42" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="B42" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="C42" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="D42" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E42" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F42" s="6" t="str">
         <f t="shared" si="0"/>
@@ -2347,19 +2182,19 @@
     </row>
     <row r="43" spans="1:7" ht="22.05" customHeight="1">
       <c r="A43" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="C43" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="D43" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="E43" s="8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F43" s="6" t="str">
         <f t="shared" si="0"/>
@@ -2367,45 +2202,22 @@
       </c>
       <c r="G43" s="7"/>
     </row>
-    <row r="44" spans="1:7" ht="22.05" customHeight="1">
-      <c r="A44" t="s">
-        <v>46</v>
-      </c>
-      <c r="B44" t="s">
-        <v>47</v>
-      </c>
-      <c r="C44" t="s">
-        <v>50</v>
-      </c>
-      <c r="D44" t="s">
-        <v>51</v>
-      </c>
-      <c r="E44" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="F44" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>OK</v>
-      </c>
-      <c r="G44" s="7"/>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="D46" t="s">
-        <v>62</v>
-      </c>
-      <c r="E46">
-        <f>COUNTIF(F5:F44,"OK")</f>
+    <row r="45" spans="1:7">
+      <c r="D45" t="s">
+        <v>45</v>
+      </c>
+      <c r="E45">
+        <f>COUNTIF(F4:F43,"OK")</f>
         <v>40</v>
       </c>
-      <c r="F46" t="str">
-        <f>IF(E46=40,"ЗАПОЛНЕНО","ПРОВЕРИТЬ")</f>
+      <c r="F45" t="str">
+        <f>IF(E45=40,"ЗАПОЛНЕНО","ПРОВЕРИТЬ")</f>
         <v>ЗАПОЛНЕНО</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A3:G3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
